--- a/语音/风机故障.xlsx
+++ b/语音/风机故障.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="1号水轮机调速器巡检" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>序号</t>
   </si>
@@ -68,10 +68,10 @@
     <t>操作完成</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置，“冷却故障”“硅柜限制”指示灯点亮</t>
-  </si>
-  <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置</t>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置，“冷却故障”“硅柜限制”指示灯点亮</t>
+  </si>
+  <si>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置</t>
   </si>
   <si>
     <t>“冷却故障”“硅柜限制”指示灯点亮</t>
@@ -110,15 +110,12 @@
     <t>已打开可控硅1号整流柜柜门</t>
   </si>
   <si>
-    <t>将可控硅1号整流柜风机电源空气开关分闸</t>
+    <t>将可控硅1号整流柜风机电源空气开关和备用电源空气开关分闸</t>
   </si>
   <si>
     <t>风机电源空气开关分闸</t>
   </si>
   <si>
-    <t>将可控硅1号整流柜风机备用电源空气开关分闸</t>
-  </si>
-  <si>
     <t>风机备用电源空气开关分闸</t>
   </si>
   <si>
@@ -128,15 +125,12 @@
     <t>已完成整流桥风机更换</t>
   </si>
   <si>
-    <t>将可控硅1号整流柜风机电源空气开关合闸</t>
+    <t>将可控硅1号整流柜风机电源空气开关和备用电源空气开关合闸</t>
   </si>
   <si>
     <t>风机电源空气开关合闸</t>
   </si>
   <si>
-    <t>将可控硅1号整流柜风机备用电源空气开关合闸</t>
-  </si>
-  <si>
     <t>风机备用电源空气开关合闸</t>
   </si>
   <si>
@@ -158,10 +152,10 @@
     <t>已关闭可控硅1号整流柜柜门</t>
   </si>
   <si>
-    <t xml:space="preserve">使用PCS-9425整流桥智能测控装置故障复位操作，命令路径：本地命令，故障复位 </t>
-  </si>
-  <si>
-    <t>使用PCS-9425整流桥智能测控装置故障复位操作</t>
+    <t xml:space="preserve">使用PCS-9425整流桥智能测控装置，故障复位操作，命令路径：本地命令，故障复位 </t>
+  </si>
+  <si>
+    <t>使用PCS-9425整流桥智能测控装置，故障复位操作</t>
   </si>
   <si>
     <t xml:space="preserve">命令路径：本地命令，故障复位 </t>
@@ -170,7 +164,7 @@
     <t>已完成故障复位操作</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置，“冷却故障”“硅柜限制”指示灯熄灭</t>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置，“冷却故障”“硅柜限制”指示灯熄灭</t>
   </si>
   <si>
     <t>“冷却故障”“硅柜限制”指示灯熄灭</t>
@@ -189,6 +183,9 @@
   </si>
   <si>
     <t>已完成可控硅1号整流柜整流桥风机故障处理</t>
+  </si>
+  <si>
+    <t>已完成可控硅1号整流柜面板指示灯检查</t>
   </si>
 </sst>
 </file>
@@ -822,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,13 +828,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1222,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.0083333333333" customWidth="1"/>
@@ -1252,16 +1246,16 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1270,11 +1264,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1283,11 +1277,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1296,11 +1290,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1309,13 +1303,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1324,11 +1318,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1337,11 +1331,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1350,13 +1344,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1365,11 +1359,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1378,11 +1372,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1391,13 +1385,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1406,11 +1400,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1419,11 +1413,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1432,13 +1426,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1447,11 +1441,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1460,13 +1454,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1475,315 +1469,293 @@
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" ht="30.5" customHeight="1" spans="1:5">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>2</v>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" ht="30.5" customHeight="1" spans="1:5">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>12</v>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="30.5" customHeight="1" spans="1:5">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>2</v>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" ht="30.5" customHeight="1" spans="1:5">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>12</v>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="30.5" customHeight="1" spans="1:5">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>2</v>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24" ht="30.5" customHeight="1" spans="1:5">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" ht="30.5" customHeight="1" spans="1:5">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="30.5" customHeight="1" spans="1:5">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>12</v>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="27" ht="30.5" customHeight="1" spans="1:5">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>2</v>
+      <c r="E27" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="30.5" customHeight="1" spans="1:5">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>9</v>
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="30.5" customHeight="1" spans="1:5">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" ht="30.5" customHeight="1" spans="1:5">
+    <row r="30" ht="47" customHeight="1" spans="1:5">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="D30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="31" ht="30.5" customHeight="1" spans="1:5">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A32" s="2">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" ht="47" customHeight="1" spans="1:5">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="3" t="s">
+    <row r="33" ht="47" customHeight="1" spans="1:5">
+      <c r="A33" s="2">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="33" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="34" ht="30.5" customHeight="1" spans="1:5">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="3" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A35" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="35" ht="47" customHeight="1" spans="1:5">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="36" ht="30.5" customHeight="1" spans="1:5">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>9</v>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="30.5" customHeight="1" spans="1:5">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>12</v>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38" ht="30.5" customHeight="1" spans="1:5">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="3" t="s">
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:5">
+      <c r="D39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="E39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1791,7 +1763,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E40" numberStoredAsText="1"/>
+    <ignoredError sqref="A37:D38 E36 A36:C36 A34:E35 E33 A33:B33 A7:E16 A17:B17 E17 A18:E21 A22:B22 E22 A23:E29 A30:B30 E30 A31:E32 E6 A6:B6 A1:E5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>